--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -71,7 +71,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -118,11 +118,6 @@
         <fgColor rgb="00ED7D31"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -150,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -198,9 +193,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +616,7 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3. なお不足している項目は14件（R-1〜R-14）です。このうち「定めなければならない事項」に関わるものが3件（R-2・R-3・R-6）、「定めるよう努めなければならない事項」が4件（R-1・R-4・R-5・R-10）です。</t>
+          <t>3. なお不足していた項目は14件（R-1〜R-14）でした。このうち優先度「高」の4件（R-1〜R-4）とR-8を令和8年9月24日に反映しています。このうち「定めなければならない事項」に関わるものが3件（R-2・R-3・R-6）、「定めるよう努めなければならない事項」が4件（R-1・R-4・R-5・R-10）です。</t>
         </is>
       </c>
     </row>
@@ -766,7 +758,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>計画に必要な語が実際に本文へ現れているかを機械的に数えたものです。0は、その事項が計画に書かれていないことを意味します。</t>
+          <t>計画に必要な語が実際に本文へ現れているかを機械的に数えたものです。0は、その事項が計画に書かれていないことを意味します。骨子案の列はレビュー時点（令和8年9月17日）のまま動きません。計画素案の列は現在の値であり、令和8年9月24日に反映した分が入っています。</t>
         </is>
       </c>
     </row>
@@ -783,7 +775,8 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>計画素案</t>
+          <t>計画素案
+（現在）</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -801,8 +794,8 @@
       <c r="B21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>0</v>
+      <c r="C21" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
@@ -819,8 +812,8 @@
       <c r="B22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>0</v>
+      <c r="C22" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
@@ -837,8 +830,8 @@
       <c r="B23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="7" t="n">
-        <v>0</v>
+      <c r="C23" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
@@ -855,8 +848,8 @@
       <c r="B24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>0</v>
+      <c r="C24" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
@@ -874,7 +867,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
@@ -891,8 +884,8 @@
       <c r="B26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>0</v>
+      <c r="C26" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -909,8 +902,8 @@
       <c r="B27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>0</v>
+      <c r="C27" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
@@ -927,8 +920,8 @@
       <c r="B28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>0</v>
+      <c r="C28" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
@@ -945,8 +938,8 @@
       <c r="B29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="7" t="n">
-        <v>0</v>
+      <c r="C29" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
@@ -963,8 +956,8 @@
       <c r="B30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>0</v>
+      <c r="C30" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -975,7 +968,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>圏域単位</t>
+          <t>計画的な基盤整備</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
@@ -986,7 +979,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>別表第二 三㈠④・三㈡③</t>
+          <t>別表第二 三㈠④・三㈡③（圏域単位を標準とした見通し）</t>
         </is>
       </c>
     </row>
@@ -1000,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
@@ -1144,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
@@ -1216,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
@@ -1410,12 +1403,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>第4章（４）</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>一部</t>
+          <t>第4章（４）。目標表に「医療的ケア児等に関する協議の場の設置」を追加（令和8年9月24日）</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>素案で補充</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1558,7 +1551,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>なし（R-5として整理。優先度 中）</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -1596,7 +1589,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>第4章（２）の本文に、県の別表第四による算定を勘案して定める旨を記載</t>
+          <t>第4章（２）の目標表に行を追加（令和8年9月24日）。値は県の算定値待ち</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -1785,13 +1778,13 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>第1章6に庁内関係課と自立支援協議会の役割分担はあるが、
-就労関係機関との連携方法の記述はない</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>不足</t>
+          <t>第5章14 関係機関との連携を新設（令和8年9月24日）。就労・教育・保健医療・
+保育子育て・相談支援・権利擁護・防災の11機関と連携の内容を一覧にした</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>素案で補充</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1866,12 +1859,13 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>なし。第4章（７）に成果目標はあるが、記載事項としての節はない</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>改正で新規</t>
+          <t>第5章13 障がい福祉人材の確保・定着、生産性向上及び経営基盤の確立を新設
+（令和8年9月24日）。①〜④の4区分と意思決定支援の推進を記載</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>素案で補充</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2413,7 +2407,7 @@
           <t>骨子案・素案とも記載なし</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>R-1　第5章に1節を新設する</t>
         </is>
@@ -2445,7 +2439,7 @@
           <t>骨子案・素案とも記載なし</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>R-1に含めて整理。県計画の該当箇所を確認</t>
         </is>
@@ -2477,7 +2471,7 @@
           <t>骨子案14か所・素案22か所とも「自立支援協議会」「協議会」のまま</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>R-7　初出に法律上の名称を注記する（村の条例・要綱の名称は変えない）</t>
         </is>
@@ -2509,7 +2503,7 @@
           <t>素案 第5章9に「第三の二の3」の引用あり（この引用自体は変更なし）</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>R-9　別表第二を引用する箇所を確認して番号を更新</t>
         </is>
@@ -2542,7 +2536,7 @@
           <t>骨子案・素案とも「医療的ケア者」0か所</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>R-3　用語の定義を第8章4 用語解説に追加し、第4章（４）・第5章2に反映</t>
         </is>
@@ -2574,7 +2568,7 @@
           <t>素案は本文に協議の場の必要性を書いているが、目標表の行がない</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>R-3　第4章（４）の目標表に「医療的ケア児等に関する協議の場の設置」の行を追加</t>
         </is>
@@ -2606,7 +2600,7 @@
           <t>素案は配置目標のみで役割の記述がない</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>R-3　配置に加えて役割（養成研修の修了、圏域配置の可否）を記述</t>
         </is>
@@ -2638,7 +2632,7 @@
           <t>素案は個別避難計画に3か所触れているが、県のセンターとの接続はない</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>R-3　第4章（４）又は第5章9（地域生活支援事業）で接続を書く</t>
         </is>
@@ -2670,7 +2664,7 @@
           <t>サービス見込量ブック 11_告示別表第一根拠 に「重度者は内数として別掲」と整理済みだが、計画本文の見込量表には行がない</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>R-10　村の実績データ受領後、第5章4・5の表に内数の行を追加</t>
         </is>
@@ -2702,7 +2696,7 @@
           <t>サービス見込量ブック 11 に反映済み</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>R-10に含めて表記を更新</t>
         </is>
@@ -2734,7 +2728,7 @@
           <t>素案 第5章9の移動支援の注記で地区の分散に触れているが、ニーズ把握の方針はない</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>R-11　第2章8（アンケート調査）又は第5章1に地区単位の把握の方針を書く</t>
         </is>
@@ -3510,7 +3504,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>優先度「高」は、計画の確定までに必ず埋める必要がある項目です。</t>
+          <t>優先度「高」の4件とR-8は令和8年9月24日に反映済みです（対応方針の末尾を参照）。</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3578,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>第5章に1節を新設する。①障害福祉サービス・相談支援、②障害児通所支援・障害児相談支援、③地域生活支援事業の従事者、④地域生活支援事業の生産性向上の4区分で、県のワンストップ窓口・処遇改善加算の取得促進・研修受講の後押しなど村が実際にできる取組を書く。成果目標（７）と対にする</t>
+          <t>第5章に1節を新設する。①障害福祉サービス・相談支援、②障害児通所支援・障害児相談支援、③地域生活支援事業の従事者、④地域生活支援事業の生産性向上の4区分で、県のワンストップ窓口・処遇改善加算の取得促進・研修受講の後押しなど村が実際にできる取組を書く。成果目標（７）と対にする【令和8年9月24日 反映済】第5章13として新設。①障害福祉サービス・相談支援、②障害児通所支援・障害児相談支援、③地域生活支援事業の従事者、④地域生活支援事業の生産性向上の4区分と、意思決定支援の推進（R-8）を記載した。</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -3626,7 +3620,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>県の第8期障がい福祉計画の算定値を照会し、本村の基盤整備量（利用者数）を確定する。県計画の公表が本村の計画確定に間に合わない場合の取扱いも県に確認する</t>
+          <t>県の第8期障がい福祉計画の算定値を照会し、本村の基盤整備量（利用者数）を確定する。県計画の公表が本村の計画確定に間に合わない場合の取扱いも県に確認する【令和8年9月24日 枠を反映】第4章（２）の目標表に行を追加し、本文で算定の仕組みを説明した。値は県の算定値待ちのため【県の算定値待ち】と表示している（Q-1）。</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -3668,7 +3662,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>①用語解説に医療的ケア者・医療的ケア児等を追加 ②第4章（４）の目標表に「医療的ケア児等に関する協議の場の設置」の行を追加 ③コーディネーターの要件（養成研修修了、圏域配置可）と役割を記述 ④法律名・センター名を改正後の名称に統一 ⑤医療的ケア児1人が18歳到達後も医療的ケア者として対象になることを第5章2に反映</t>
+          <t>①用語解説に医療的ケア者・医療的ケア児等を追加 ②第4章（４）の目標表に「医療的ケア児等に関する協議の場の設置」の行を追加 ③コーディネーターの要件（養成研修修了、圏域配置可）と役割を記述 ④法律名・センター名を改正後の名称に統一 ⑤医療的ケア児1人が18歳到達後も医療的ケア者として対象になることを第5章2に反映【令和8年9月24日 反映済】第4章（４）の目標表に協議の場の設置を追加し、法改正の内容・コーディネーターの要件と役割・県のセンターとの接続を本文に記載。第5章2に18歳到達時の医療的ケア児等の扱いを新設。用語解説に5語を追加した。</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -3710,7 +3704,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>第5章又は第7章に「関係機関との連携」の節を設け、会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター、特別支援学校、医療機関、こども家庭センターとの連携方法を一覧にする。成果目標（３）一般就労への移行の実効性を支える記述になる</t>
+          <t>第5章又は第7章に「関係機関との連携」の節を設け、会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター、特別支援学校、医療機関、こども家庭センターとの連携方法を一覧にする。成果目標（３）一般就労への移行の実効性を支える記述になる【令和8年9月24日 反映済】第5章14として新設。就労（ハローワーク・障害者職業センター・障害者就業生活支援センター）、教育、保健医療、保育子育て、相談支援、権利擁護、防災の11機関と連携の内容を一覧にした。</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -3845,7 +3839,7 @@
           <t>1行</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -3879,7 +3873,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>成果目標（７）及びR-1の節で、村内事業所への意思決定支援ガイドラインの周知と、相談支援専門員・サービス管理責任者の研修受講の後押しを書く。用語解説にも追加する</t>
+          <t>成果目標（７）及びR-1の節で、村内事業所への意思決定支援ガイドラインの周知と、相談支援専門員・サービス管理責任者の研修受講の後押しを書く。用語解説にも追加する【令和8年9月24日 反映済】第5章13の「■意思決定支援の推進」として記載した。</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -3929,7 +3923,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="19" t="inlineStr">
         <is>
           <t>低</t>
         </is>

--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>

--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
@@ -1028,8 +1028,8 @@
       <c r="B34" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
+      <c r="C34" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>

--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -1119,7 +1119,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>

--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>

--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>

--- a/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
+++ b/output/北塩原村_骨子案レビュー_基本指針網羅性.xlsx
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
